--- a/Auditorias_Clientes/Bata/Bata 29/09-03/Reporte_Auditoria_Maestro_Bata.xlsx
+++ b/Auditorias_Clientes/Bata/Bata 29/09-03/Reporte_Auditoria_Maestro_Bata.xlsx
@@ -1453,7 +1453,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="16659225" cy="6191250"/>
+    <ext cx="9324975" cy="6191250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1533,7 +1533,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10896600" cy="6191250"/>
+    <ext cx="6181725" cy="6181725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1558,7 +1558,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10896600" cy="6191250"/>
+    <ext cx="6181725" cy="6181725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1608,7 +1608,7 @@
       <row>79</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7753350" cy="6181725"/>
+    <ext cx="6181725" cy="6191250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1633,7 +1633,7 @@
       <row>79</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7753350" cy="6181725"/>
+    <ext cx="6181725" cy="6191250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1716,6 +1716,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6181725" cy="6181725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>185</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6181725" cy="6191250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>185</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6181725" cy="6191250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1821,156 +1896,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>201</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>226</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2101,156 +2026,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>152</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>202</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>252</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6181725" cy="6191250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2761,7 +2536,7 @@
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="47" t="inlineStr">
         <is>
-          <t>Entrada Princial</t>
+          <t>Exploracion 1</t>
         </is>
       </c>
       <c r="B3" s="47" t="inlineStr">
@@ -2775,10 +2550,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="48" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" s="48" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H3" s="49">
         <f>IF(F3&gt;0, G3/F3, 0)</f>
@@ -2792,7 +2567,7 @@
         <v/>
       </c>
       <c r="K3" s="48" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L3" s="49">
         <f>IF(F3&gt;0, K3/F3, 0)</f>
@@ -2806,42 +2581,42 @@
         <v/>
       </c>
       <c r="O3" s="48" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="P3" s="49">
         <f>IF(G3&gt;0, O3/G3, 0)</f>
         <v/>
       </c>
       <c r="Q3" s="48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R3" s="49">
         <f>IF(G3&gt;0, Q3/G3, 0)</f>
         <v/>
       </c>
       <c r="S3" s="48" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T3" s="49">
         <f>IF(G3&gt;0, S3/G3, 0)</f>
         <v/>
       </c>
       <c r="U3" s="48" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V3" s="49">
         <f>IF(S3&gt;0, U3/S3, "")</f>
         <v/>
       </c>
       <c r="W3" s="48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X3" s="49">
         <f>IF(G3&gt;0, W3/G3, 0)</f>
         <v/>
       </c>
       <c r="Y3" s="48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="49">
         <f>IF(W3&gt;0, Y3/W3, "")</f>
@@ -2851,7 +2626,7 @@
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
         <is>
-          <t>Entrada-Izquierda</t>
+          <t>Interior 1</t>
         </is>
       </c>
       <c r="B4" s="47" t="inlineStr">
@@ -2862,13 +2637,13 @@
       <c r="C4" s="47" t="inlineStr"/>
       <c r="D4" s="47" t="inlineStr"/>
       <c r="E4" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G4" s="48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H4" s="49">
         <f>IF(F4&gt;0, G4/F4, 0)</f>
@@ -2882,7 +2657,7 @@
         <v/>
       </c>
       <c r="K4" s="48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L4" s="49">
         <f>IF(F4&gt;0, K4/F4, 0)</f>
@@ -2896,42 +2671,42 @@
         <v/>
       </c>
       <c r="O4" s="48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P4" s="49">
         <f>IF(G4&gt;0, O4/G4, 0)</f>
         <v/>
       </c>
       <c r="Q4" s="48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R4" s="49">
         <f>IF(G4&gt;0, Q4/G4, 0)</f>
         <v/>
       </c>
       <c r="S4" s="48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T4" s="49">
         <f>IF(G4&gt;0, S4/G4, 0)</f>
         <v/>
       </c>
       <c r="U4" s="48" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="V4" s="49">
         <f>IF(S4&gt;0, U4/S4, "")</f>
         <v/>
       </c>
       <c r="W4" s="48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X4" s="49">
         <f>IF(G4&gt;0, W4/G4, 0)</f>
         <v/>
       </c>
       <c r="Y4" s="48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="49">
         <f>IF(W4&gt;0, Y4/W4, "")</f>
@@ -2941,7 +2716,7 @@
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="47" t="inlineStr">
         <is>
-          <t>Exploracion-Izq</t>
+          <t>Estanteria Principal</t>
         </is>
       </c>
       <c r="B5" s="47" t="inlineStr">
@@ -2952,76 +2727,76 @@
       <c r="C5" s="47" t="inlineStr"/>
       <c r="D5" s="47" t="inlineStr"/>
       <c r="E5" s="47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H5" s="49">
         <f>IF(F5&gt;0, G5/F5, 0)</f>
         <v/>
       </c>
       <c r="I5" s="48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" s="49">
         <f>IF(F5&gt;0, I5/F5, 0)</f>
         <v/>
       </c>
       <c r="K5" s="48" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L5" s="49">
         <f>IF(F5&gt;0, K5/F5, 0)</f>
         <v/>
       </c>
       <c r="M5" s="48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="49">
         <f>IF(G5&gt;0, M5/G5, 0)</f>
         <v/>
       </c>
       <c r="O5" s="48" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="P5" s="49">
         <f>IF(G5&gt;0, O5/G5, 0)</f>
         <v/>
       </c>
       <c r="Q5" s="48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R5" s="49">
         <f>IF(G5&gt;0, Q5/G5, 0)</f>
         <v/>
       </c>
       <c r="S5" s="48" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T5" s="49">
         <f>IF(G5&gt;0, S5/G5, 0)</f>
         <v/>
       </c>
       <c r="U5" s="48" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V5" s="49">
         <f>IF(S5&gt;0, U5/S5, "")</f>
         <v/>
       </c>
       <c r="W5" s="48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X5" s="49">
         <f>IF(G5&gt;0, W5/G5, 0)</f>
         <v/>
       </c>
       <c r="Y5" s="48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="49">
         <f>IF(W5&gt;0, Y5/W5, "")</f>
@@ -3031,7 +2806,7 @@
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="47" t="inlineStr">
         <is>
-          <t>Exterior-2</t>
+          <t>Interior 2</t>
         </is>
       </c>
       <c r="B6" s="47" t="inlineStr">
@@ -3042,27 +2817,27 @@
       <c r="C6" s="47" t="inlineStr"/>
       <c r="D6" s="47" t="inlineStr"/>
       <c r="E6" s="47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="48" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H6" s="49">
         <f>IF(F6&gt;0, G6/F6, 0)</f>
         <v/>
       </c>
       <c r="I6" s="48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J6" s="49">
         <f>IF(F6&gt;0, I6/F6, 0)</f>
         <v/>
       </c>
       <c r="K6" s="48" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L6" s="49">
         <f>IF(F6&gt;0, K6/F6, 0)</f>
@@ -3076,42 +2851,42 @@
         <v/>
       </c>
       <c r="O6" s="48" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P6" s="49">
         <f>IF(G6&gt;0, O6/G6, 0)</f>
         <v/>
       </c>
       <c r="Q6" s="48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" s="49">
         <f>IF(G6&gt;0, Q6/G6, 0)</f>
         <v/>
       </c>
       <c r="S6" s="48" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T6" s="49">
         <f>IF(G6&gt;0, S6/G6, 0)</f>
         <v/>
       </c>
       <c r="U6" s="48" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V6" s="49">
         <f>IF(S6&gt;0, U6/S6, "")</f>
         <v/>
       </c>
       <c r="W6" s="48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X6" s="49">
         <f>IF(G6&gt;0, W6/G6, 0)</f>
         <v/>
       </c>
       <c r="Y6" s="48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="49">
         <f>IF(W6&gt;0, Y6/W6, "")</f>
@@ -3119,632 +2894,268 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
-          <t>Exterior-L</t>
+          <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>09-03</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr"/>
-      <c r="D7" s="47" t="inlineStr"/>
-      <c r="E7" s="47" t="n">
-        <v>1</v>
+      <c r="C7" s="50" t="inlineStr"/>
+      <c r="D7" s="50" t="inlineStr"/>
+      <c r="E7" s="50" t="inlineStr"/>
+      <c r="F7" s="51" t="n">
+        <v>70</v>
       </c>
-      <c r="F7" s="48" t="n">
-        <v>22</v>
+      <c r="G7" s="51" t="n">
+        <v>64</v>
       </c>
-      <c r="G7" s="48" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="49">
+      <c r="H7" s="52">
         <f>IF(F7&gt;0, G7/F7, 0)</f>
         <v/>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I7" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="49">
+      <c r="J7" s="52">
         <f>IF(F7&gt;0, I7/F7, 0)</f>
         <v/>
       </c>
-      <c r="K7" s="48" t="n">
-        <v>16</v>
+      <c r="K7" s="51" t="n">
+        <v>64</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="52">
         <f>IF(F7&gt;0, K7/F7, 0)</f>
         <v/>
       </c>
-      <c r="M7" s="48" t="n">
+      <c r="M7" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="49">
+      <c r="N7" s="52">
         <f>IF(G7&gt;0, M7/G7, 0)</f>
         <v/>
       </c>
-      <c r="O7" s="48" t="n">
-        <v>6</v>
+      <c r="O7" s="51" t="n">
+        <v>64</v>
       </c>
-      <c r="P7" s="49">
+      <c r="P7" s="52">
         <f>IF(G7&gt;0, O7/G7, 0)</f>
         <v/>
       </c>
-      <c r="Q7" s="48" t="n">
-        <v>10</v>
+      <c r="Q7" s="51" t="n">
+        <v>0</v>
       </c>
-      <c r="R7" s="49">
+      <c r="R7" s="52">
         <f>IF(G7&gt;0, Q7/G7, 0)</f>
         <v/>
       </c>
-      <c r="S7" s="48" t="n">
-        <v>16</v>
+      <c r="S7" s="51" t="n">
+        <v>64</v>
       </c>
-      <c r="T7" s="49">
+      <c r="T7" s="52">
         <f>IF(G7&gt;0, S7/G7, 0)</f>
         <v/>
       </c>
-      <c r="U7" s="48" t="n">
-        <v>15</v>
+      <c r="U7" s="51" t="n">
+        <v>61</v>
       </c>
-      <c r="V7" s="49">
+      <c r="V7" s="52">
         <f>IF(S7&gt;0, U7/S7, "")</f>
         <v/>
       </c>
-      <c r="W7" s="48" t="n">
-        <v>16</v>
+      <c r="W7" s="51" t="n">
+        <v>0</v>
       </c>
-      <c r="X7" s="49">
+      <c r="X7" s="52">
         <f>IF(G7&gt;0, W7/G7, 0)</f>
         <v/>
       </c>
-      <c r="Y7" s="48" t="n">
-        <v>15</v>
+      <c r="Y7" s="51" t="n">
+        <v>0</v>
       </c>
-      <c r="Z7" s="49">
+      <c r="Z7" s="52">
         <f>IF(W7&gt;0, Y7/W7, "")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="6" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Decision-Der</t>
+          <t>END</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="13" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="12" t="n"/>
+      <c r="V11" s="14" t="n"/>
+      <c r="W11" s="15" t="n"/>
+      <c r="X11" s="14" t="n"/>
+      <c r="Y11" s="12" t="n"/>
+      <c r="Z11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="16" t="n"/>
+      <c r="W12" s="16" t="n"/>
+      <c r="X12" s="16" t="n"/>
+      <c r="Y12" s="16" t="n"/>
+      <c r="Z12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>09-03</t>
+          <t>TOTALES</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr"/>
-      <c r="D8" s="47" t="inlineStr"/>
-      <c r="E8" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" s="49">
-        <f>IF(F8&gt;0, G8/F8, 0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="49">
-        <f>IF(F8&gt;0, I8/F8, 0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="L8" s="49">
-        <f>IF(F8&gt;0, K8/F8, 0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="49">
-        <f>IF(G8&gt;0, M8/G8, 0)</f>
-        <v/>
-      </c>
-      <c r="O8" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="49">
-        <f>IF(G8&gt;0, O8/G8, 0)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="48" t="n">
-        <v>10</v>
-      </c>
-      <c r="R8" s="49">
-        <f>IF(G8&gt;0, Q8/G8, 0)</f>
-        <v/>
-      </c>
-      <c r="S8" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" s="49">
-        <f>IF(G8&gt;0, S8/G8, 0)</f>
-        <v/>
-      </c>
-      <c r="U8" s="48" t="n">
-        <v>10</v>
-      </c>
-      <c r="V8" s="49">
-        <f>IF(S8&gt;0, U8/S8, "")</f>
-        <v/>
-      </c>
-      <c r="W8" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="X8" s="49">
-        <f>IF(G8&gt;0, W8/G8, 0)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="48" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z8" s="49">
-        <f>IF(W8&gt;0, Y8/W8, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>Decision-Izq</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>09-03</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="inlineStr"/>
-      <c r="D9" s="47" t="inlineStr"/>
-      <c r="E9" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="G9" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="H9" s="49">
-        <f>IF(F9&gt;0, G9/F9, 0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="49">
-        <f>IF(F9&gt;0, I9/F9, 0)</f>
-        <v/>
-      </c>
-      <c r="K9" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="L9" s="49">
-        <f>IF(F9&gt;0, K9/F9, 0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="49">
-        <f>IF(G9&gt;0, M9/G9, 0)</f>
-        <v/>
-      </c>
-      <c r="O9" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="49">
-        <f>IF(G9&gt;0, O9/G9, 0)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="48" t="n">
-        <v>24</v>
-      </c>
-      <c r="R9" s="49">
-        <f>IF(G9&gt;0, Q9/G9, 0)</f>
-        <v/>
-      </c>
-      <c r="S9" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="T9" s="49">
-        <f>IF(G9&gt;0, S9/G9, 0)</f>
-        <v/>
-      </c>
-      <c r="U9" s="48" t="n">
-        <v>26</v>
-      </c>
-      <c r="V9" s="49">
-        <f>IF(S9&gt;0, U9/S9, "")</f>
-        <v/>
-      </c>
-      <c r="W9" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="X9" s="49">
-        <f>IF(G9&gt;0, W9/G9, 0)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="48" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z9" s="49">
-        <f>IF(W9&gt;0, Y9/W9, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>Zona-Caja</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>09-03</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr"/>
-      <c r="D10" s="47" t="inlineStr"/>
-      <c r="E10" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="49">
-        <f>IF(F10&gt;0, G10/F10, 0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="49">
-        <f>IF(F10&gt;0, I10/F10, 0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="49">
-        <f>IF(F10&gt;0, K10/F10, 0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="49">
-        <f>IF(G10&gt;0, M10/G10, 0)</f>
-        <v/>
-      </c>
-      <c r="O10" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="P10" s="49">
-        <f>IF(G10&gt;0, O10/G10, 0)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="49">
-        <f>IF(G10&gt;0, Q10/G10, 0)</f>
-        <v/>
-      </c>
-      <c r="S10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" s="49">
-        <f>IF(G10&gt;0, S10/G10, 0)</f>
-        <v/>
-      </c>
-      <c r="U10" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="49">
-        <f>IF(S10&gt;0, U10/S10, "")</f>
-        <v/>
-      </c>
-      <c r="W10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" s="49">
-        <f>IF(G10&gt;0, W10/G10, 0)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="49">
-        <f>IF(W10&gt;0, Y10/W10, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>Interior-Der</t>
-        </is>
-      </c>
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t>09-03</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr"/>
-      <c r="D11" s="47" t="inlineStr"/>
-      <c r="E11" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="G11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="H11" s="49">
-        <f>IF(F11&gt;0, G11/F11, 0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="49">
-        <f>IF(F11&gt;0, I11/F11, 0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="L11" s="49">
-        <f>IF(F11&gt;0, K11/F11, 0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="49">
-        <f>IF(G11&gt;0, M11/G11, 0)</f>
-        <v/>
-      </c>
-      <c r="O11" s="48" t="n">
-        <v>21</v>
-      </c>
-      <c r="P11" s="49">
-        <f>IF(G11&gt;0, O11/G11, 0)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="48" t="n">
-        <v>14</v>
-      </c>
-      <c r="R11" s="49">
-        <f>IF(G11&gt;0, Q11/G11, 0)</f>
-        <v/>
-      </c>
-      <c r="S11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="T11" s="49">
-        <f>IF(G11&gt;0, S11/G11, 0)</f>
-        <v/>
-      </c>
-      <c r="U11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="V11" s="49">
-        <f>IF(S11&gt;0, U11/S11, "")</f>
-        <v/>
-      </c>
-      <c r="W11" s="48" t="n">
-        <v>35</v>
-      </c>
-      <c r="X11" s="49">
-        <f>IF(G11&gt;0, W11/G11, 0)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="48" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z11" s="49">
-        <f>IF(W11&gt;0, Y11/W11, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>Interior-Izq</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>09-03</t>
-        </is>
-      </c>
-      <c r="C12" s="47" t="inlineStr"/>
-      <c r="D12" s="47" t="inlineStr"/>
-      <c r="E12" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="H12" s="49">
-        <f>IF(F12&gt;0, G12/F12, 0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="49">
-        <f>IF(F12&gt;0, I12/F12, 0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="L12" s="49">
-        <f>IF(F12&gt;0, K12/F12, 0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="49">
-        <f>IF(G12&gt;0, M12/G12, 0)</f>
-        <v/>
-      </c>
-      <c r="O12" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" s="49">
-        <f>IF(G12&gt;0, O12/G12, 0)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="R12" s="49">
-        <f>IF(G12&gt;0, Q12/G12, 0)</f>
-        <v/>
-      </c>
-      <c r="S12" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="T12" s="49">
-        <f>IF(G12&gt;0, S12/G12, 0)</f>
-        <v/>
-      </c>
-      <c r="U12" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="V12" s="49">
-        <f>IF(S12&gt;0, U12/S12, "")</f>
-        <v/>
-      </c>
-      <c r="W12" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="X12" s="49">
-        <f>IF(G12&gt;0, W12/G12, 0)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z12" s="49">
-        <f>IF(W12&gt;0, Y12/W12, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="50" t="inlineStr">
-        <is>
-          <t>09-03</t>
-        </is>
-      </c>
-      <c r="C13" s="50" t="inlineStr"/>
-      <c r="D13" s="50" t="inlineStr"/>
-      <c r="E13" s="50" t="inlineStr"/>
-      <c r="F13" s="51" t="n">
-        <v>178</v>
-      </c>
-      <c r="G13" s="51" t="n">
-        <v>158</v>
-      </c>
-      <c r="H13" s="52">
-        <f>IF(F13&gt;0, G13/F13, 0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="51" t="n">
-        <v>20</v>
-      </c>
-      <c r="J13" s="52">
-        <f>IF(F13&gt;0, I13/F13, 0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="51" t="n">
-        <v>157</v>
-      </c>
-      <c r="L13" s="52">
-        <f>IF(F13&gt;0, K13/F13, 0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="52">
-        <f>IF(G13&gt;0, M13/G13, 0)</f>
-        <v/>
-      </c>
-      <c r="O13" s="51" t="n">
-        <v>58</v>
-      </c>
-      <c r="P13" s="52">
-        <f>IF(G13&gt;0, O13/G13, 0)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="51" t="n">
-        <v>100</v>
-      </c>
-      <c r="R13" s="52">
-        <f>IF(G13&gt;0, Q13/G13, 0)</f>
-        <v/>
-      </c>
-      <c r="S13" s="51" t="n">
-        <v>156</v>
-      </c>
-      <c r="T13" s="52">
-        <f>IF(G13&gt;0, S13/G13, 0)</f>
-        <v/>
-      </c>
-      <c r="U13" s="51" t="n">
-        <v>143</v>
-      </c>
-      <c r="V13" s="52">
-        <f>IF(S13&gt;0, U13/S13, "")</f>
-        <v/>
-      </c>
-      <c r="W13" s="51" t="n">
-        <v>156</v>
-      </c>
-      <c r="X13" s="52">
-        <f>IF(G13&gt;0, W13/G13, 0)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="51" t="n">
-        <v>131</v>
-      </c>
-      <c r="Z13" s="52">
-        <f>IF(W13&gt;0, Y13/W13, "")</f>
-        <v/>
-      </c>
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="38" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="38" t="n"/>
+      <c r="Q13" s="38" t="n"/>
+      <c r="R13" s="38" t="n"/>
+      <c r="S13" s="38" t="n"/>
+      <c r="T13" s="38" t="n"/>
+      <c r="U13" s="38" t="n"/>
+      <c r="V13" s="38" t="n"/>
+      <c r="W13" s="38" t="n"/>
+      <c r="X13" s="38" t="n"/>
+      <c r="Y13" s="38" t="n"/>
+      <c r="Z13" s="39" t="n"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="16" t="n"/>
